--- a/output/pdf_financials_xlsx/MYR.xlsx
+++ b/output/pdf_financials_xlsx/MYR.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.75895</v>
+        <v>-0.75895</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.328186</v>
+        <v>-0.328186</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.410948</v>
+        <v>-0.410948</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.75895</v>
+        <v>-0.75895</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.328186</v>
+        <v>-0.328186</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.410948</v>
+        <v>-0.410948</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.75895</v>
+        <v>-0.75895</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.328186</v>
+        <v>-0.328186</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.410948</v>
+        <v>-0.410948</v>
       </c>
     </row>
     <row r="24">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-25.298333</v>
+        <v>25.298333</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.75895</v>
+        <v>-0.75895</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.328186</v>
+        <v>-0.328186</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.410948</v>
+        <v>-0.410948</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.75895</v>
+        <v>-0.75895</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.328186</v>
+        <v>-0.328186</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.410948</v>
+        <v>-0.410948</v>
       </c>
     </row>
     <row r="30">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.75895</v>
+        <v>-0.75895</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.328186</v>
+        <v>-0.328186</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.410948</v>
+        <v>-0.410948</v>
       </c>
     </row>
     <row r="29">

--- a/output/pdf_financials_xlsx/MYR.xlsx
+++ b/output/pdf_financials_xlsx/MYR.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.069913</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.020195</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.016706</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.069913</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.020195</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.016706</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.069913</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.031445</v>
+        <v>0.01125</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.043623</v>
+        <v>0.026917</v>
       </c>
     </row>
     <row r="49">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
